--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
+    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="551">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44439,7 +44439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
+    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -2362,6 +2362,569 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I1" t="s">
+        <v>488</v>
+      </c>
+      <c r="J1" t="s">
+        <v>489</v>
+      </c>
+      <c r="K1" t="s">
+        <v>490</v>
+      </c>
+      <c r="L1" t="s">
+        <v>491</v>
+      </c>
+      <c r="M1" t="s">
+        <v>492</v>
+      </c>
+      <c r="N1" t="s">
+        <v>493</v>
+      </c>
+      <c r="O1" t="s">
+        <v>494</v>
+      </c>
+      <c r="P1" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>521</v>
+      </c>
+      <c r="I2" t="s">
+        <v>531</v>
+      </c>
+      <c r="J2" t="s">
+        <v>541</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>512</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>522</v>
+      </c>
+      <c r="I3" t="s">
+        <v>532</v>
+      </c>
+      <c r="J3" t="s">
+        <v>542</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>513</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>523</v>
+      </c>
+      <c r="I4" t="s">
+        <v>533</v>
+      </c>
+      <c r="J4" t="s">
+        <v>543</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>514</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>524</v>
+      </c>
+      <c r="I5" t="s">
+        <v>534</v>
+      </c>
+      <c r="J5" t="s">
+        <v>544</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>515</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>525</v>
+      </c>
+      <c r="I6" t="s">
+        <v>535</v>
+      </c>
+      <c r="J6" t="s">
+        <v>545</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>498</v>
+      </c>
+      <c r="B7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>526</v>
+      </c>
+      <c r="I7" t="s">
+        <v>536</v>
+      </c>
+      <c r="J7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>527</v>
+      </c>
+      <c r="I8" t="s">
+        <v>537</v>
+      </c>
+      <c r="J8" t="s">
+        <v>547</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B9" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>518</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>528</v>
+      </c>
+      <c r="I9" t="s">
+        <v>538</v>
+      </c>
+      <c r="J9" t="s">
+        <v>548</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>500</v>
+      </c>
+      <c r="B10" t="s">
+        <v>509</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>519</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>529</v>
+      </c>
+      <c r="I10" t="s">
+        <v>539</v>
+      </c>
+      <c r="J10" t="s">
+        <v>549</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>500</v>
+      </c>
+      <c r="B11" t="s">
+        <v>510</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>520</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>530</v>
+      </c>
+      <c r="I11" t="s">
+        <v>540</v>
+      </c>
+      <c r="J11" t="s">
+        <v>550</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -44437,567 +45000,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B1" t="s">
-        <v>481</v>
-      </c>
-      <c r="C1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D1" t="s">
-        <v>483</v>
-      </c>
-      <c r="E1" t="s">
-        <v>484</v>
-      </c>
-      <c r="F1" t="s">
-        <v>485</v>
-      </c>
-      <c r="G1" t="s">
-        <v>486</v>
-      </c>
-      <c r="H1" t="s">
-        <v>487</v>
-      </c>
-      <c r="I1" t="s">
-        <v>488</v>
-      </c>
-      <c r="J1" t="s">
-        <v>489</v>
-      </c>
-      <c r="K1" t="s">
-        <v>490</v>
-      </c>
-      <c r="L1" t="s">
-        <v>491</v>
-      </c>
-      <c r="M1" t="s">
-        <v>492</v>
-      </c>
-      <c r="N1" t="s">
-        <v>493</v>
-      </c>
-      <c r="O1" t="s">
-        <v>494</v>
-      </c>
-      <c r="P1" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I2" t="s">
-        <v>531</v>
-      </c>
-      <c r="J2" t="s">
-        <v>541</v>
-      </c>
-      <c r="K2" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>497</v>
-      </c>
-      <c r="B3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>512</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>522</v>
-      </c>
-      <c r="I3" t="s">
-        <v>532</v>
-      </c>
-      <c r="J3" t="s">
-        <v>542</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>497</v>
-      </c>
-      <c r="B4" t="s">
-        <v>503</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>513</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>523</v>
-      </c>
-      <c r="I4" t="s">
-        <v>533</v>
-      </c>
-      <c r="J4" t="s">
-        <v>543</v>
-      </c>
-      <c r="K4" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>497</v>
-      </c>
-      <c r="B5" t="s">
-        <v>504</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>514</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H5" t="s">
-        <v>524</v>
-      </c>
-      <c r="I5" t="s">
-        <v>534</v>
-      </c>
-      <c r="J5" t="s">
-        <v>544</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>497</v>
-      </c>
-      <c r="B6" t="s">
-        <v>505</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>515</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>525</v>
-      </c>
-      <c r="I6" t="s">
-        <v>535</v>
-      </c>
-      <c r="J6" t="s">
-        <v>545</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>498</v>
-      </c>
-      <c r="B7" t="s">
-        <v>506</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>516</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>526</v>
-      </c>
-      <c r="I7" t="s">
-        <v>536</v>
-      </c>
-      <c r="J7" t="s">
-        <v>546</v>
-      </c>
-      <c r="K7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.497</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.194</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>499</v>
-      </c>
-      <c r="B8" t="s">
-        <v>507</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>517</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>527</v>
-      </c>
-      <c r="I8" t="s">
-        <v>537</v>
-      </c>
-      <c r="J8" t="s">
-        <v>547</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.642</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>499</v>
-      </c>
-      <c r="B9" t="s">
-        <v>508</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>518</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>528</v>
-      </c>
-      <c r="I9" t="s">
-        <v>538</v>
-      </c>
-      <c r="J9" t="s">
-        <v>548</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B10" t="s">
-        <v>509</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>519</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H10" t="s">
-        <v>529</v>
-      </c>
-      <c r="I10" t="s">
-        <v>539</v>
-      </c>
-      <c r="J10" t="s">
-        <v>549</v>
-      </c>
-      <c r="K10" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.719</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>500</v>
-      </c>
-      <c r="B11" t="s">
-        <v>510</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>520</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H11" t="s">
-        <v>530</v>
-      </c>
-      <c r="I11" t="s">
-        <v>540</v>
-      </c>
-      <c r="J11" t="s">
-        <v>550</v>
-      </c>
-      <c r="K11" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.419</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
+    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
   </sheets>
 </workbook>
 </file>
@@ -2362,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
+    <sheet name="Stand2" sheetId="14" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
@@ -2362,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="14" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="15"/>
+    <sheet name="Stand2" sheetId="16" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="17"/>
   </sheets>
 </workbook>
 </file>
@@ -2362,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
+    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="635">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -61655,7 +61655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
+    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="676">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -71078,7 +71078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
+    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -3057,6 +3057,1069 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E1" t="s">
+        <v>576</v>
+      </c>
+      <c r="F1" t="s">
+        <v>577</v>
+      </c>
+      <c r="G1" t="s">
+        <v>578</v>
+      </c>
+      <c r="H1" t="s">
+        <v>579</v>
+      </c>
+      <c r="I1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J1" t="s">
+        <v>581</v>
+      </c>
+      <c r="K1" t="s">
+        <v>582</v>
+      </c>
+      <c r="L1" t="s">
+        <v>583</v>
+      </c>
+      <c r="M1" t="s">
+        <v>584</v>
+      </c>
+      <c r="N1" t="s">
+        <v>585</v>
+      </c>
+      <c r="O1" t="s">
+        <v>586</v>
+      </c>
+      <c r="P1" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>616</v>
+      </c>
+      <c r="I2" t="s">
+        <v>636</v>
+      </c>
+      <c r="J2" t="s">
+        <v>656</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>617</v>
+      </c>
+      <c r="I3" t="s">
+        <v>637</v>
+      </c>
+      <c r="J3" t="s">
+        <v>657</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>610</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>618</v>
+      </c>
+      <c r="I4" t="s">
+        <v>638</v>
+      </c>
+      <c r="J4" t="s">
+        <v>658</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B5" t="s">
+        <v>599</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>609</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>619</v>
+      </c>
+      <c r="I5" t="s">
+        <v>639</v>
+      </c>
+      <c r="J5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>608</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>620</v>
+      </c>
+      <c r="I6" t="s">
+        <v>640</v>
+      </c>
+      <c r="J6" t="s">
+        <v>660</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B7" t="s">
+        <v>601</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>606</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>621</v>
+      </c>
+      <c r="I7" t="s">
+        <v>641</v>
+      </c>
+      <c r="J7" t="s">
+        <v>661</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" t="s">
+        <v>602</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>614</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>622</v>
+      </c>
+      <c r="I8" t="s">
+        <v>642</v>
+      </c>
+      <c r="J8" t="s">
+        <v>662</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>591</v>
+      </c>
+      <c r="B9" t="s">
+        <v>603</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>615</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>623</v>
+      </c>
+      <c r="I9" t="s">
+        <v>643</v>
+      </c>
+      <c r="J9" t="s">
+        <v>663</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>592</v>
+      </c>
+      <c r="B10" t="s">
+        <v>604</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>607</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>624</v>
+      </c>
+      <c r="I10" t="s">
+        <v>644</v>
+      </c>
+      <c r="J10" t="s">
+        <v>664</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B11" t="s">
+        <v>605</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>612</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>625</v>
+      </c>
+      <c r="I11" t="s">
+        <v>645</v>
+      </c>
+      <c r="J11" t="s">
+        <v>665</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>593</v>
+      </c>
+      <c r="B12" t="s">
+        <v>606</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>605</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I12" t="s">
+        <v>646</v>
+      </c>
+      <c r="J12" t="s">
+        <v>666</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>593</v>
+      </c>
+      <c r="B13" t="s">
+        <v>607</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>603</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>627</v>
+      </c>
+      <c r="I13" t="s">
+        <v>647</v>
+      </c>
+      <c r="J13" t="s">
+        <v>667</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>593</v>
+      </c>
+      <c r="B14" t="s">
+        <v>608</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>601</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>628</v>
+      </c>
+      <c r="I14" t="s">
+        <v>648</v>
+      </c>
+      <c r="J14" t="s">
+        <v>668</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>593</v>
+      </c>
+      <c r="B15" t="s">
+        <v>609</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>600</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>629</v>
+      </c>
+      <c r="I15" t="s">
+        <v>649</v>
+      </c>
+      <c r="J15" t="s">
+        <v>669</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>593</v>
+      </c>
+      <c r="B16" t="s">
+        <v>610</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>596</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>630</v>
+      </c>
+      <c r="I16" t="s">
+        <v>650</v>
+      </c>
+      <c r="J16" t="s">
+        <v>670</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>593</v>
+      </c>
+      <c r="B17" t="s">
+        <v>611</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>602</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>631</v>
+      </c>
+      <c r="I17" t="s">
+        <v>651</v>
+      </c>
+      <c r="J17" t="s">
+        <v>671</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>594</v>
+      </c>
+      <c r="B18" t="s">
+        <v>612</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>599</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>632</v>
+      </c>
+      <c r="I18" t="s">
+        <v>652</v>
+      </c>
+      <c r="J18" t="s">
+        <v>672</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>595</v>
+      </c>
+      <c r="B19" t="s">
+        <v>613</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>597</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>633</v>
+      </c>
+      <c r="I19" t="s">
+        <v>653</v>
+      </c>
+      <c r="J19" t="s">
+        <v>673</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>595</v>
+      </c>
+      <c r="B20" t="s">
+        <v>614</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>604</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>634</v>
+      </c>
+      <c r="I20" t="s">
+        <v>654</v>
+      </c>
+      <c r="J20" t="s">
+        <v>674</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>595</v>
+      </c>
+      <c r="B21" t="s">
+        <v>615</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>598</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>635</v>
+      </c>
+      <c r="I21" t="s">
+        <v>655</v>
+      </c>
+      <c r="J21" t="s">
+        <v>675</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -71076,1061 +72139,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>572</v>
-      </c>
-      <c r="B1" t="s">
-        <v>573</v>
-      </c>
-      <c r="C1" t="s">
-        <v>574</v>
-      </c>
-      <c r="D1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E1" t="s">
-        <v>576</v>
-      </c>
-      <c r="F1" t="s">
-        <v>577</v>
-      </c>
-      <c r="G1" t="s">
-        <v>578</v>
-      </c>
-      <c r="H1" t="s">
-        <v>579</v>
-      </c>
-      <c r="I1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J1" t="s">
-        <v>581</v>
-      </c>
-      <c r="K1" t="s">
-        <v>582</v>
-      </c>
-      <c r="L1" t="s">
-        <v>583</v>
-      </c>
-      <c r="M1" t="s">
-        <v>584</v>
-      </c>
-      <c r="N1" t="s">
-        <v>585</v>
-      </c>
-      <c r="O1" t="s">
-        <v>586</v>
-      </c>
-      <c r="P1" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>589</v>
-      </c>
-      <c r="B2" t="s">
-        <v>596</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I2" t="s">
-        <v>636</v>
-      </c>
-      <c r="J2" t="s">
-        <v>656</v>
-      </c>
-      <c r="K2" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>589</v>
-      </c>
-      <c r="B3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>611</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>617</v>
-      </c>
-      <c r="I3" t="s">
-        <v>637</v>
-      </c>
-      <c r="J3" t="s">
-        <v>657</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>589</v>
-      </c>
-      <c r="B4" t="s">
-        <v>598</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>610</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>618</v>
-      </c>
-      <c r="I4" t="s">
-        <v>638</v>
-      </c>
-      <c r="J4" t="s">
-        <v>658</v>
-      </c>
-      <c r="K4" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>589</v>
-      </c>
-      <c r="B5" t="s">
-        <v>599</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>609</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H5" t="s">
-        <v>619</v>
-      </c>
-      <c r="I5" t="s">
-        <v>639</v>
-      </c>
-      <c r="J5" t="s">
-        <v>659</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>589</v>
-      </c>
-      <c r="B6" t="s">
-        <v>600</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>608</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>620</v>
-      </c>
-      <c r="I6" t="s">
-        <v>640</v>
-      </c>
-      <c r="J6" t="s">
-        <v>660</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>590</v>
-      </c>
-      <c r="B7" t="s">
-        <v>601</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>606</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>621</v>
-      </c>
-      <c r="I7" t="s">
-        <v>641</v>
-      </c>
-      <c r="J7" t="s">
-        <v>661</v>
-      </c>
-      <c r="K7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.497</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.194</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>591</v>
-      </c>
-      <c r="B8" t="s">
-        <v>602</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>614</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>622</v>
-      </c>
-      <c r="I8" t="s">
-        <v>642</v>
-      </c>
-      <c r="J8" t="s">
-        <v>662</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.642</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>591</v>
-      </c>
-      <c r="B9" t="s">
-        <v>603</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>615</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>623</v>
-      </c>
-      <c r="I9" t="s">
-        <v>643</v>
-      </c>
-      <c r="J9" t="s">
-        <v>663</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>592</v>
-      </c>
-      <c r="B10" t="s">
-        <v>604</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>607</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H10" t="s">
-        <v>624</v>
-      </c>
-      <c r="I10" t="s">
-        <v>644</v>
-      </c>
-      <c r="J10" t="s">
-        <v>664</v>
-      </c>
-      <c r="K10" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.719</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>592</v>
-      </c>
-      <c r="B11" t="s">
-        <v>605</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>612</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H11" t="s">
-        <v>625</v>
-      </c>
-      <c r="I11" t="s">
-        <v>645</v>
-      </c>
-      <c r="J11" t="s">
-        <v>665</v>
-      </c>
-      <c r="K11" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.419</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>593</v>
-      </c>
-      <c r="B12" t="s">
-        <v>606</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E12" t="s">
-        <v>605</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H12" t="s">
-        <v>626</v>
-      </c>
-      <c r="I12" t="s">
-        <v>646</v>
-      </c>
-      <c r="J12" t="s">
-        <v>666</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>593</v>
-      </c>
-      <c r="B13" t="s">
-        <v>607</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>603</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>627</v>
-      </c>
-      <c r="I13" t="s">
-        <v>647</v>
-      </c>
-      <c r="J13" t="s">
-        <v>667</v>
-      </c>
-      <c r="K13" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>593</v>
-      </c>
-      <c r="B14" t="s">
-        <v>608</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>601</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="H14" t="s">
-        <v>628</v>
-      </c>
-      <c r="I14" t="s">
-        <v>648</v>
-      </c>
-      <c r="J14" t="s">
-        <v>668</v>
-      </c>
-      <c r="K14" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.576</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>593</v>
-      </c>
-      <c r="B15" t="s">
-        <v>609</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>600</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H15" t="s">
-        <v>629</v>
-      </c>
-      <c r="I15" t="s">
-        <v>649</v>
-      </c>
-      <c r="J15" t="s">
-        <v>669</v>
-      </c>
-      <c r="K15" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>593</v>
-      </c>
-      <c r="B16" t="s">
-        <v>610</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>596</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="H16" t="s">
-        <v>630</v>
-      </c>
-      <c r="I16" t="s">
-        <v>650</v>
-      </c>
-      <c r="J16" t="s">
-        <v>670</v>
-      </c>
-      <c r="K16" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.546</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.699</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>593</v>
-      </c>
-      <c r="B17" t="s">
-        <v>611</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>602</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H17" t="s">
-        <v>631</v>
-      </c>
-      <c r="I17" t="s">
-        <v>651</v>
-      </c>
-      <c r="J17" t="s">
-        <v>671</v>
-      </c>
-      <c r="K17" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.152</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>594</v>
-      </c>
-      <c r="B18" t="s">
-        <v>612</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>599</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H18" t="s">
-        <v>632</v>
-      </c>
-      <c r="I18" t="s">
-        <v>652</v>
-      </c>
-      <c r="J18" t="s">
-        <v>672</v>
-      </c>
-      <c r="K18" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>595</v>
-      </c>
-      <c r="B19" t="s">
-        <v>613</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>597</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="H19" t="s">
-        <v>633</v>
-      </c>
-      <c r="I19" t="s">
-        <v>653</v>
-      </c>
-      <c r="J19" t="s">
-        <v>673</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.825</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>595</v>
-      </c>
-      <c r="B20" t="s">
-        <v>614</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>604</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H20" t="s">
-        <v>634</v>
-      </c>
-      <c r="I20" t="s">
-        <v>654</v>
-      </c>
-      <c r="J20" t="s">
-        <v>674</v>
-      </c>
-      <c r="K20" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.621</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>595</v>
-      </c>
-      <c r="B21" t="s">
-        <v>615</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>598</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="H21" t="s">
-        <v>635</v>
-      </c>
-      <c r="I21" t="s">
-        <v>655</v>
-      </c>
-      <c r="J21" t="s">
-        <v>675</v>
-      </c>
-      <c r="K21" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.708</v>
-      </c>
-      <c r="O21"/>
-      <c r="P21"/>
-      <c r="Q21"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
+    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
   </sheets>
 </workbook>
 </file>
@@ -3057,7 +3057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
+    <sheet name="Stand2" sheetId="14" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
@@ -3057,7 +3057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
+    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="790">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -95377,7 +95377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
+    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -3719,6 +3719,1610 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C1" t="s">
+        <v>652</v>
+      </c>
+      <c r="D1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E1" t="s">
+        <v>654</v>
+      </c>
+      <c r="F1" t="s">
+        <v>655</v>
+      </c>
+      <c r="G1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I1" t="s">
+        <v>658</v>
+      </c>
+      <c r="J1" t="s">
+        <v>659</v>
+      </c>
+      <c r="K1" t="s">
+        <v>660</v>
+      </c>
+      <c r="L1" t="s">
+        <v>661</v>
+      </c>
+      <c r="M1" t="s">
+        <v>662</v>
+      </c>
+      <c r="N1" t="s">
+        <v>663</v>
+      </c>
+      <c r="O1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P1" t="s">
+        <v>665</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>695</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>700</v>
+      </c>
+      <c r="I2" t="s">
+        <v>730</v>
+      </c>
+      <c r="J2" t="s">
+        <v>760</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>693</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>701</v>
+      </c>
+      <c r="I3" t="s">
+        <v>731</v>
+      </c>
+      <c r="J3" t="s">
+        <v>761</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>692</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>702</v>
+      </c>
+      <c r="I4" t="s">
+        <v>732</v>
+      </c>
+      <c r="J4" t="s">
+        <v>762</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>667</v>
+      </c>
+      <c r="B5" t="s">
+        <v>681</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>691</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>703</v>
+      </c>
+      <c r="I5" t="s">
+        <v>733</v>
+      </c>
+      <c r="J5" t="s">
+        <v>763</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>667</v>
+      </c>
+      <c r="B6" t="s">
+        <v>682</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>690</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>704</v>
+      </c>
+      <c r="I6" t="s">
+        <v>734</v>
+      </c>
+      <c r="J6" t="s">
+        <v>764</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>688</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>705</v>
+      </c>
+      <c r="I7" t="s">
+        <v>735</v>
+      </c>
+      <c r="J7" t="s">
+        <v>765</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>669</v>
+      </c>
+      <c r="B8" t="s">
+        <v>684</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>696</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>706</v>
+      </c>
+      <c r="I8" t="s">
+        <v>736</v>
+      </c>
+      <c r="J8" t="s">
+        <v>766</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>669</v>
+      </c>
+      <c r="B9" t="s">
+        <v>685</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>697</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>707</v>
+      </c>
+      <c r="I9" t="s">
+        <v>737</v>
+      </c>
+      <c r="J9" t="s">
+        <v>767</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>670</v>
+      </c>
+      <c r="B10" t="s">
+        <v>686</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>689</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>708</v>
+      </c>
+      <c r="I10" t="s">
+        <v>738</v>
+      </c>
+      <c r="J10" t="s">
+        <v>768</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>670</v>
+      </c>
+      <c r="B11" t="s">
+        <v>687</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>694</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>709</v>
+      </c>
+      <c r="I11" t="s">
+        <v>739</v>
+      </c>
+      <c r="J11" t="s">
+        <v>769</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>671</v>
+      </c>
+      <c r="B12" t="s">
+        <v>688</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>687</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>710</v>
+      </c>
+      <c r="I12" t="s">
+        <v>740</v>
+      </c>
+      <c r="J12" t="s">
+        <v>770</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>671</v>
+      </c>
+      <c r="B13" t="s">
+        <v>689</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>685</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>711</v>
+      </c>
+      <c r="I13" t="s">
+        <v>741</v>
+      </c>
+      <c r="J13" t="s">
+        <v>771</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>671</v>
+      </c>
+      <c r="B14" t="s">
+        <v>690</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>683</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>712</v>
+      </c>
+      <c r="I14" t="s">
+        <v>742</v>
+      </c>
+      <c r="J14" t="s">
+        <v>772</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>671</v>
+      </c>
+      <c r="B15" t="s">
+        <v>691</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>682</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>713</v>
+      </c>
+      <c r="I15" t="s">
+        <v>743</v>
+      </c>
+      <c r="J15" t="s">
+        <v>773</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>671</v>
+      </c>
+      <c r="B16" t="s">
+        <v>692</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>678</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>714</v>
+      </c>
+      <c r="I16" t="s">
+        <v>744</v>
+      </c>
+      <c r="J16" t="s">
+        <v>774</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>671</v>
+      </c>
+      <c r="B17" t="s">
+        <v>693</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>684</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>715</v>
+      </c>
+      <c r="I17" t="s">
+        <v>745</v>
+      </c>
+      <c r="J17" t="s">
+        <v>775</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B18" t="s">
+        <v>694</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>681</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>716</v>
+      </c>
+      <c r="I18" t="s">
+        <v>746</v>
+      </c>
+      <c r="J18" t="s">
+        <v>776</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>673</v>
+      </c>
+      <c r="B19" t="s">
+        <v>695</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>679</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>717</v>
+      </c>
+      <c r="I19" t="s">
+        <v>747</v>
+      </c>
+      <c r="J19" t="s">
+        <v>777</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>673</v>
+      </c>
+      <c r="B20" t="s">
+        <v>696</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>686</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>718</v>
+      </c>
+      <c r="I20" t="s">
+        <v>748</v>
+      </c>
+      <c r="J20" t="s">
+        <v>778</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>673</v>
+      </c>
+      <c r="B21" t="s">
+        <v>697</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>719</v>
+      </c>
+      <c r="I21" t="s">
+        <v>749</v>
+      </c>
+      <c r="J21" t="s">
+        <v>779</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>674</v>
+      </c>
+      <c r="B22" t="s">
+        <v>683</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>689</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>720</v>
+      </c>
+      <c r="I22" t="s">
+        <v>750</v>
+      </c>
+      <c r="J22" t="s">
+        <v>780</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>674</v>
+      </c>
+      <c r="B23" t="s">
+        <v>678</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>699</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H23" t="s">
+        <v>721</v>
+      </c>
+      <c r="I23" t="s">
+        <v>751</v>
+      </c>
+      <c r="J23" t="s">
+        <v>781</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>674</v>
+      </c>
+      <c r="B24" t="s">
+        <v>679</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>686</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>722</v>
+      </c>
+      <c r="I24" t="s">
+        <v>752</v>
+      </c>
+      <c r="J24" t="s">
+        <v>782</v>
+      </c>
+      <c r="K24" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>674</v>
+      </c>
+      <c r="B25" t="s">
+        <v>684</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>692</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H25" t="s">
+        <v>723</v>
+      </c>
+      <c r="I25" t="s">
+        <v>753</v>
+      </c>
+      <c r="J25" t="s">
+        <v>783</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>674</v>
+      </c>
+      <c r="B26" t="s">
+        <v>698</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>694</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H26" t="s">
+        <v>724</v>
+      </c>
+      <c r="I26" t="s">
+        <v>754</v>
+      </c>
+      <c r="J26" t="s">
+        <v>784</v>
+      </c>
+      <c r="K26" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>674</v>
+      </c>
+      <c r="B27" t="s">
+        <v>680</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>688</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H27" t="s">
+        <v>725</v>
+      </c>
+      <c r="I27" t="s">
+        <v>755</v>
+      </c>
+      <c r="J27" t="s">
+        <v>785</v>
+      </c>
+      <c r="K27" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>675</v>
+      </c>
+      <c r="B28" t="s">
+        <v>691</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>695</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>726</v>
+      </c>
+      <c r="I28" t="s">
+        <v>756</v>
+      </c>
+      <c r="J28" t="s">
+        <v>786</v>
+      </c>
+      <c r="K28" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>676</v>
+      </c>
+      <c r="B29" t="s">
+        <v>682</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>696</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H29" t="s">
+        <v>727</v>
+      </c>
+      <c r="I29" t="s">
+        <v>757</v>
+      </c>
+      <c r="J29" t="s">
+        <v>787</v>
+      </c>
+      <c r="K29" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>677</v>
+      </c>
+      <c r="B30" t="s">
+        <v>697</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>690</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H30" t="s">
+        <v>728</v>
+      </c>
+      <c r="I30" t="s">
+        <v>758</v>
+      </c>
+      <c r="J30" t="s">
+        <v>788</v>
+      </c>
+      <c r="K30" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>677</v>
+      </c>
+      <c r="B31" t="s">
+        <v>687</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>681</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H31" t="s">
+        <v>729</v>
+      </c>
+      <c r="I31" t="s">
+        <v>759</v>
+      </c>
+      <c r="J31" t="s">
+        <v>789</v>
+      </c>
+      <c r="K31" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>677</v>
+      </c>
+      <c r="B32" t="s">
+        <v>687</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>681</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H32" t="s">
+        <v>729</v>
+      </c>
+      <c r="I32" t="s">
+        <v>759</v>
+      </c>
+      <c r="J32" t="s">
+        <v>789</v>
+      </c>
+      <c r="K32" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -95375,1608 +96979,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>650</v>
-      </c>
-      <c r="B1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C1" t="s">
-        <v>652</v>
-      </c>
-      <c r="D1" t="s">
-        <v>653</v>
-      </c>
-      <c r="E1" t="s">
-        <v>654</v>
-      </c>
-      <c r="F1" t="s">
-        <v>655</v>
-      </c>
-      <c r="G1" t="s">
-        <v>656</v>
-      </c>
-      <c r="H1" t="s">
-        <v>657</v>
-      </c>
-      <c r="I1" t="s">
-        <v>658</v>
-      </c>
-      <c r="J1" t="s">
-        <v>659</v>
-      </c>
-      <c r="K1" t="s">
-        <v>660</v>
-      </c>
-      <c r="L1" t="s">
-        <v>661</v>
-      </c>
-      <c r="M1" t="s">
-        <v>662</v>
-      </c>
-      <c r="N1" t="s">
-        <v>663</v>
-      </c>
-      <c r="O1" t="s">
-        <v>664</v>
-      </c>
-      <c r="P1" t="s">
-        <v>665</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>667</v>
-      </c>
-      <c r="B2" t="s">
-        <v>678</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>695</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H2" t="s">
-        <v>700</v>
-      </c>
-      <c r="I2" t="s">
-        <v>730</v>
-      </c>
-      <c r="J2" t="s">
-        <v>760</v>
-      </c>
-      <c r="K2" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>667</v>
-      </c>
-      <c r="B3" t="s">
-        <v>679</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>693</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>701</v>
-      </c>
-      <c r="I3" t="s">
-        <v>731</v>
-      </c>
-      <c r="J3" t="s">
-        <v>761</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>667</v>
-      </c>
-      <c r="B4" t="s">
-        <v>680</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>692</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>702</v>
-      </c>
-      <c r="I4" t="s">
-        <v>732</v>
-      </c>
-      <c r="J4" t="s">
-        <v>762</v>
-      </c>
-      <c r="K4" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>667</v>
-      </c>
-      <c r="B5" t="s">
-        <v>681</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>691</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H5" t="s">
-        <v>703</v>
-      </c>
-      <c r="I5" t="s">
-        <v>733</v>
-      </c>
-      <c r="J5" t="s">
-        <v>763</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>667</v>
-      </c>
-      <c r="B6" t="s">
-        <v>682</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>690</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>704</v>
-      </c>
-      <c r="I6" t="s">
-        <v>734</v>
-      </c>
-      <c r="J6" t="s">
-        <v>764</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>668</v>
-      </c>
-      <c r="B7" t="s">
-        <v>683</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>688</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>705</v>
-      </c>
-      <c r="I7" t="s">
-        <v>735</v>
-      </c>
-      <c r="J7" t="s">
-        <v>765</v>
-      </c>
-      <c r="K7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.497</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.194</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>669</v>
-      </c>
-      <c r="B8" t="s">
-        <v>684</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>696</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>706</v>
-      </c>
-      <c r="I8" t="s">
-        <v>736</v>
-      </c>
-      <c r="J8" t="s">
-        <v>766</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.642</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>669</v>
-      </c>
-      <c r="B9" t="s">
-        <v>685</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>697</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>707</v>
-      </c>
-      <c r="I9" t="s">
-        <v>737</v>
-      </c>
-      <c r="J9" t="s">
-        <v>767</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>670</v>
-      </c>
-      <c r="B10" t="s">
-        <v>686</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>689</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H10" t="s">
-        <v>708</v>
-      </c>
-      <c r="I10" t="s">
-        <v>738</v>
-      </c>
-      <c r="J10" t="s">
-        <v>768</v>
-      </c>
-      <c r="K10" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.719</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>670</v>
-      </c>
-      <c r="B11" t="s">
-        <v>687</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>694</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H11" t="s">
-        <v>709</v>
-      </c>
-      <c r="I11" t="s">
-        <v>739</v>
-      </c>
-      <c r="J11" t="s">
-        <v>769</v>
-      </c>
-      <c r="K11" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.419</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>671</v>
-      </c>
-      <c r="B12" t="s">
-        <v>688</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E12" t="s">
-        <v>687</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H12" t="s">
-        <v>710</v>
-      </c>
-      <c r="I12" t="s">
-        <v>740</v>
-      </c>
-      <c r="J12" t="s">
-        <v>770</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>671</v>
-      </c>
-      <c r="B13" t="s">
-        <v>689</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>685</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>711</v>
-      </c>
-      <c r="I13" t="s">
-        <v>741</v>
-      </c>
-      <c r="J13" t="s">
-        <v>771</v>
-      </c>
-      <c r="K13" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>671</v>
-      </c>
-      <c r="B14" t="s">
-        <v>690</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>683</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="H14" t="s">
-        <v>712</v>
-      </c>
-      <c r="I14" t="s">
-        <v>742</v>
-      </c>
-      <c r="J14" t="s">
-        <v>772</v>
-      </c>
-      <c r="K14" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.576</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>671</v>
-      </c>
-      <c r="B15" t="s">
-        <v>691</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>682</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H15" t="s">
-        <v>713</v>
-      </c>
-      <c r="I15" t="s">
-        <v>743</v>
-      </c>
-      <c r="J15" t="s">
-        <v>773</v>
-      </c>
-      <c r="K15" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>671</v>
-      </c>
-      <c r="B16" t="s">
-        <v>692</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>678</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="H16" t="s">
-        <v>714</v>
-      </c>
-      <c r="I16" t="s">
-        <v>744</v>
-      </c>
-      <c r="J16" t="s">
-        <v>774</v>
-      </c>
-      <c r="K16" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.546</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.699</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>671</v>
-      </c>
-      <c r="B17" t="s">
-        <v>693</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>684</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H17" t="s">
-        <v>715</v>
-      </c>
-      <c r="I17" t="s">
-        <v>745</v>
-      </c>
-      <c r="J17" t="s">
-        <v>775</v>
-      </c>
-      <c r="K17" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.152</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>672</v>
-      </c>
-      <c r="B18" t="s">
-        <v>694</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>681</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H18" t="s">
-        <v>716</v>
-      </c>
-      <c r="I18" t="s">
-        <v>746</v>
-      </c>
-      <c r="J18" t="s">
-        <v>776</v>
-      </c>
-      <c r="K18" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>673</v>
-      </c>
-      <c r="B19" t="s">
-        <v>695</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>679</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="H19" t="s">
-        <v>717</v>
-      </c>
-      <c r="I19" t="s">
-        <v>747</v>
-      </c>
-      <c r="J19" t="s">
-        <v>777</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.825</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>673</v>
-      </c>
-      <c r="B20" t="s">
-        <v>696</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>686</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H20" t="s">
-        <v>718</v>
-      </c>
-      <c r="I20" t="s">
-        <v>748</v>
-      </c>
-      <c r="J20" t="s">
-        <v>778</v>
-      </c>
-      <c r="K20" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.621</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>673</v>
-      </c>
-      <c r="B21" t="s">
-        <v>697</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>680</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="H21" t="s">
-        <v>719</v>
-      </c>
-      <c r="I21" t="s">
-        <v>749</v>
-      </c>
-      <c r="J21" t="s">
-        <v>779</v>
-      </c>
-      <c r="K21" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.708</v>
-      </c>
-      <c r="O21"/>
-      <c r="P21"/>
-      <c r="Q21"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>674</v>
-      </c>
-      <c r="B22" t="s">
-        <v>683</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>689</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H22" t="s">
-        <v>720</v>
-      </c>
-      <c r="I22" t="s">
-        <v>750</v>
-      </c>
-      <c r="J22" t="s">
-        <v>780</v>
-      </c>
-      <c r="K22" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.869</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>674</v>
-      </c>
-      <c r="B23" t="s">
-        <v>678</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>699</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H23" t="s">
-        <v>721</v>
-      </c>
-      <c r="I23" t="s">
-        <v>751</v>
-      </c>
-      <c r="J23" t="s">
-        <v>781</v>
-      </c>
-      <c r="K23" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.194</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="O23"/>
-      <c r="P23"/>
-      <c r="Q23"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>674</v>
-      </c>
-      <c r="B24" t="s">
-        <v>679</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>686</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H24" t="s">
-        <v>722</v>
-      </c>
-      <c r="I24" t="s">
-        <v>752</v>
-      </c>
-      <c r="J24" t="s">
-        <v>782</v>
-      </c>
-      <c r="K24" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.575</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.806</v>
-      </c>
-      <c r="P24" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>674</v>
-      </c>
-      <c r="B25" t="s">
-        <v>684</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>692</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H25" t="s">
-        <v>723</v>
-      </c>
-      <c r="I25" t="s">
-        <v>753</v>
-      </c>
-      <c r="J25" t="s">
-        <v>783</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.367</v>
-      </c>
-      <c r="O25"/>
-      <c r="P25"/>
-      <c r="Q25"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>674</v>
-      </c>
-      <c r="B26" t="s">
-        <v>698</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>694</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H26" t="s">
-        <v>724</v>
-      </c>
-      <c r="I26" t="s">
-        <v>754</v>
-      </c>
-      <c r="J26" t="s">
-        <v>784</v>
-      </c>
-      <c r="K26" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>674</v>
-      </c>
-      <c r="B27" t="s">
-        <v>680</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E27" t="s">
-        <v>688</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H27" t="s">
-        <v>725</v>
-      </c>
-      <c r="I27" t="s">
-        <v>755</v>
-      </c>
-      <c r="J27" t="s">
-        <v>785</v>
-      </c>
-      <c r="K27" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.736</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="O27"/>
-      <c r="P27"/>
-      <c r="Q27"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>675</v>
-      </c>
-      <c r="B28" t="s">
-        <v>691</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>695</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H28" t="s">
-        <v>726</v>
-      </c>
-      <c r="I28" t="s">
-        <v>756</v>
-      </c>
-      <c r="J28" t="s">
-        <v>786</v>
-      </c>
-      <c r="K28" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>676</v>
-      </c>
-      <c r="B29" t="s">
-        <v>682</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>696</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H29" t="s">
-        <v>727</v>
-      </c>
-      <c r="I29" t="s">
-        <v>757</v>
-      </c>
-      <c r="J29" t="s">
-        <v>787</v>
-      </c>
-      <c r="K29" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="O29"/>
-      <c r="P29"/>
-      <c r="Q29"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>677</v>
-      </c>
-      <c r="B30" t="s">
-        <v>697</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="E30" t="s">
-        <v>690</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="H30" t="s">
-        <v>728</v>
-      </c>
-      <c r="I30" t="s">
-        <v>758</v>
-      </c>
-      <c r="J30" t="s">
-        <v>788</v>
-      </c>
-      <c r="K30" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.334</v>
-      </c>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>677</v>
-      </c>
-      <c r="B31" t="s">
-        <v>687</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>681</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H31" t="s">
-        <v>729</v>
-      </c>
-      <c r="I31" t="s">
-        <v>759</v>
-      </c>
-      <c r="J31" t="s">
-        <v>789</v>
-      </c>
-      <c r="K31" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.358</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.967</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>677</v>
-      </c>
-      <c r="B32" t="s">
-        <v>687</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>681</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H32" t="s">
-        <v>729</v>
-      </c>
-      <c r="I32" t="s">
-        <v>759</v>
-      </c>
-      <c r="J32" t="s">
-        <v>789</v>
-      </c>
-      <c r="K32" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.358</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.967</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P32" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/data/KKDBas.xlsx
+++ b/data/KKDBas.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
+    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
   </sheets>
 </workbook>
 </file>
@@ -3719,7 +3719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
